--- a/docs/UAT_새는돈찾기.xlsx
+++ b/docs/UAT_새는돈찾기.xlsx
@@ -932,7 +932,7 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>(팀명 입력)</t>
+          <t>해피너스</t>
         </is>
       </c>
       <c r="D2" s="65" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="C8" s="24" t="inlineStr">
         <is>
-          <t>카드 명세서 파일을 가진 사용자로서, 명세서를 업로드하면 반복 결제가 묶인 구독 목록(서비스명·금액·주기·다음 결제일)을 보고 싶다. 그래야 내가 매달 구독에 얼마를 쓰는지 한눈에 알 수 있다.</t>
+          <t>카드 명세서 파일을 가진 사용자로서, 명세서를 업로드하면 반복 결제가 묶인 구독 목록(서비스명·금액·주기·다음 결제일)과 월 구독 합계를 보고 싶다. 그래야 내가 매달 구독에 얼마를 쓰는지 한눈에 알 수 있다.</t>
         </is>
       </c>
       <c r="F8" s="5" t="n"/>
@@ -1034,12 +1034,12 @@
     <row r="9" ht="75" customHeight="1" s="53">
       <c r="B9" s="71" t="inlineStr">
         <is>
-          <t>AI 에이전트가 정체불명 결제의 실제 출처를 추적한다</t>
+          <t>정체불명 결제(PG사·앱마켓 표기)의 실제 출처를 추적한다</t>
         </is>
       </c>
       <c r="C9" s="24" t="inlineStr">
         <is>
-          <t>명세서에 PG사 이름만 찍힌 결제가 있는 사용자로서, 에이전트에게 그 결제가 무엇인지 물으면 실제 서비스 후보와 신뢰도, 근거를 듣고 싶다. 그래야 모르는 돈이 어디로 나가는지 확인할 수 있다.</t>
+          <t>명세서에 "토스페이먼츠", "NICE페이"처럼 결제대행사 이름만 찍힌 결제가 있는 사용자로서, 그 결제의 실제 서비스 후보와 신뢰도, 근거를 알고 싶다. 후보가 여러 개면 내가 직접 골라 확정하고 해지 방법을 안내받고 싶다.</t>
         </is>
       </c>
     </row>
@@ -5299,18 +5299,18 @@
       </c>
       <c r="D10" s="74" t="inlineStr">
         <is>
-          <t>demo_card_2026.csv
-(데모 명세서 6개월치, 구독 8건 + 일반 소비 포함)</t>
+          <t>data/demo_card_2026.csv
+(데모 명세서 6개월치 162건)</t>
         </is>
       </c>
       <c r="E10" s="74" t="inlineStr">
         <is>
-          <t>웹 대시보드 "명세서 업로드" 화면에 있음</t>
+          <t>백엔드·웹 서버 실행, 요금제 DB 로드됨(load_service_fees), 웹 대시보드 "명세서 업로드" 화면</t>
         </is>
       </c>
       <c r="F10" s="74" t="inlineStr">
         <is>
-          <t>데모 명세서 CSV 파일을 선택하고 "분석하기" 버튼 클릭</t>
+          <t>데모 명세서 CSV를 선택하고 "분석하기" 버튼 클릭</t>
         </is>
       </c>
       <c r="G10" s="75" t="inlineStr">
@@ -5320,7 +5320,7 @@
       </c>
       <c r="H10" s="74" t="inlineStr">
         <is>
-          <t>구독 목록이 표시됨: 서비스명·금액·결제주기·다음 결제일, 상단에 월 구독 합계. 일반 소비(편의점·식당 등)는 목록에 없음</t>
+          <t>구독 카드 8건 표시(Netflix, YouTube Premium, Spotify 등), "월 구독 합계 99,980원". 각 카드에 금액·주기·다음 결제일·신뢰도 표시. 일반 소비(GS25, 스타벅스 등)는 목록에 없음</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -5342,17 +5342,17 @@
       </c>
       <c r="D11" s="74" t="inlineStr">
         <is>
-          <t>sample.pdf (지원하지 않는 형식) 또는 금액 컬럼이 빠진 CSV</t>
+          <t>sample.pdf (CSV가 아닌 파일)</t>
         </is>
       </c>
       <c r="E11" s="74" t="inlineStr">
         <is>
-          <t>웹 대시보드 "명세서 업로드" 화면에 있음</t>
+          <t>백엔드·웹 서버 실행, 요금제 DB 로드됨(load_service_fees), 웹 대시보드 "명세서 업로드" 화면</t>
         </is>
       </c>
       <c r="F11" s="74" t="inlineStr">
         <is>
-          <t>지원하지 않는 파일을 업로드</t>
+          <t>PDF 파일을 선택하고 "분석하기" 버튼 클릭</t>
         </is>
       </c>
       <c r="G11" s="75" t="inlineStr">
@@ -5362,7 +5362,7 @@
       </c>
       <c r="H11" s="74" t="inlineStr">
         <is>
-          <t>안내 메시지 "지원하지 않는 명세서 형식입니다" 표시, 분석이 진행되지 않음</t>
+          <t>오류 문구 "지원하지 않는 명세서 형식입니다" 표시, 분석 결과가 나오지 않음</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -5376,7 +5376,7 @@
     <row r="12" ht="80" customHeight="1" s="53">
       <c r="B12" s="72" t="inlineStr">
         <is>
-          <t>AI 에이전트가 정체불명 결제의 실제 출처를 추적한다</t>
+          <t>정체불명 결제(PG사·앱마켓 표기)의 실제 출처를 추적한다</t>
         </is>
       </c>
       <c r="C12" s="73" t="n">
@@ -5386,12 +5386,12 @@
         <is>
           <t>가맹점명: 토스페이먼츠
 금액: 14,900원
-매월 15일 결제(3회)</t>
+매월 15일, 6회</t>
         </is>
       </c>
       <c r="E12" s="74" t="inlineStr">
         <is>
-          <t>데모 명세서 업로드 완료, Claude에 서비스 MCP 서버 연결됨</t>
+          <t>데모 명세서 업로드 완료, Claude Desktop에 MCP 서버(saedon) 등록 + 읽기 토큰(issue_token) 설정</t>
         </is>
       </c>
       <c r="F12" s="74" t="inlineStr">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="H12" s="76" t="inlineStr">
         <is>
-          <t>에이전트가 explain_charge 도구 호출 → "YouTube Premium(월 14,900원) 후보, 신뢰도 높음, 근거: 금액·월 주기 일치" 응답</t>
+          <t>에이전트가 explain_charge 호출 → "YouTube Premium 프리미엄, 신뢰도 high, 근거: 금액 14,900원 일치·매월 6회 결제" 답변. 다음 결제일 2026-11-15</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -5420,7 +5420,7 @@
     <row r="13" ht="80" customHeight="1" s="53">
       <c r="B13" s="72" t="inlineStr">
         <is>
-          <t>AI 에이전트가 정체불명 결제의 실제 출처를 추적한다</t>
+          <t>정체불명 결제(PG사·앱마켓 표기)의 실제 출처를 추적한다</t>
         </is>
       </c>
       <c r="C13" s="73" t="n">
@@ -5430,17 +5430,17 @@
         <is>
           <t>가맹점명: KG이니시스
 금액: 23,170원
-1회 결제</t>
+2026-09-07 1회</t>
         </is>
       </c>
       <c r="E13" s="74" t="inlineStr">
         <is>
-          <t>데모 명세서 업로드 완료, Claude에 MCP 서버 연결됨</t>
+          <t>데모 명세서 업로드 완료, Claude Desktop에 MCP 서버(saedon) 등록 + 읽기 토큰(issue_token) 설정</t>
         </is>
       </c>
       <c r="F13" s="74" t="inlineStr">
         <is>
-          <t>Claude에게 "KG이니시스 23,170원은 뭐야?" 질문</t>
+          <t>Claude에게 "9월 7일 KG이니시스 23,170원은 뭐야?" 질문</t>
         </is>
       </c>
       <c r="G13" s="75" t="inlineStr">
@@ -5450,7 +5450,7 @@
       </c>
       <c r="H13" s="74" t="inlineStr">
         <is>
-          <t>특정 서비스로 단정하지 않음: "반복 결제가 아니어서 구독이 아닌 일반 결제로 보임, 후보 신뢰도 낮음" 응답</t>
+          <t>구독으로 단정하지 않음: is_subscription=false, 신뢰도 low, "1회 결제 — 구독이 아닌 일반 결제로 보임" 답변</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -5464,25 +5464,27 @@
     <row r="14" ht="80" customHeight="1" s="53">
       <c r="B14" s="72" t="inlineStr">
         <is>
-          <t>AI 에이전트가 사용자 대신 구독 현황을 조회한다</t>
+          <t>정체불명 결제(PG사·앱마켓 표기)의 실제 출처를 추적한다</t>
         </is>
       </c>
       <c r="C14" s="73" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D14" s="74" t="inlineStr">
         <is>
-          <t>데모 명세서 (구독 8건)</t>
+          <t>가맹점명: NICE페이
+금액: 9,900원
+후보: Disney+ / Canva / CapCut</t>
         </is>
       </c>
       <c r="E14" s="74" t="inlineStr">
         <is>
-          <t>데모 명세서 업로드 완료, Claude에 MCP 서버 연결됨</t>
+          <t>R1 Positive 완료, 구독 목록에 "NICE페이 9,900원 · 신뢰도 중간" 카드가 있음</t>
         </is>
       </c>
       <c r="F14" s="74" t="inlineStr">
         <is>
-          <t>Claude에게 "나 지금 뭐 구독하고 있어?" 질문</t>
+          <t>후보 칩 중 "Disney+" 클릭</t>
         </is>
       </c>
       <c r="G14" s="75" t="inlineStr">
@@ -5492,7 +5494,7 @@
       </c>
       <c r="H14" s="74" t="inlineStr">
         <is>
-          <t>에이전트가 list_subscriptions 도구 호출 → 구독 8건의 서비스별 월 금액, 월 합계, 다음 결제일을 답함</t>
+          <t>카드가 Disney+로 확정되고 신뢰도 높음으로 바뀜. "해지하기" 버튼(Disney+ 해지 안내 링크)이 나타남</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5514,12 +5516,12 @@
       </c>
       <c r="D15" s="74" t="inlineStr">
         <is>
-          <t>만료되었거나 발급하지 않은 토큰</t>
+          <t>데모 명세서 (구독 8건)</t>
         </is>
       </c>
       <c r="E15" s="74" t="inlineStr">
         <is>
-          <t>Claude에 MCP 서버는 등록됐지만 사용자 토큰이 유효하지 않음</t>
+          <t>데모 명세서 업로드 완료, Claude Desktop에 MCP 서버(saedon) 등록 + 읽기 토큰(issue_token) 설정</t>
         </is>
       </c>
       <c r="F15" s="74" t="inlineStr">
@@ -5529,12 +5531,12 @@
       </c>
       <c r="G15" s="75" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="H15" s="74" t="inlineStr">
         <is>
-          <t>서버가 인증 오류 반환, 에이전트가 "서비스 연결(토큰) 확인이 필요합니다" 안내. 결제 데이터는 노출되지 않음</t>
+          <t>에이전트가 list_subscriptions 호출 → 구독 8건의 서비스별 월 금액, 월 합계 99,980원, 다음 결제일을 답함. Netflix 금액 인상(13,500 → 17,000원)도 언급 가능</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -5545,15 +5547,45 @@
       <c r="J15" s="1" t="n"/>
       <c r="K15" s="24" t="n"/>
     </row>
-    <row r="16" ht="14" customHeight="1" s="53">
-      <c r="B16" s="25" t="n"/>
-      <c r="C16" s="26" t="n"/>
-      <c r="D16" s="29" t="n"/>
-      <c r="E16" s="27" t="n"/>
-      <c r="F16" s="27" t="n"/>
-      <c r="G16" s="28" t="n"/>
-      <c r="H16" s="27" t="n"/>
-      <c r="I16" s="1" t="n"/>
+    <row r="16" ht="80" customHeight="1" s="53">
+      <c r="B16" s="72" t="inlineStr">
+        <is>
+          <t>AI 에이전트가 사용자 대신 구독 현황을 조회한다</t>
+        </is>
+      </c>
+      <c r="C16" s="73" t="n">
+        <v>3</v>
+      </c>
+      <c r="D16" s="76" t="inlineStr">
+        <is>
+          <t>잘못된 토큰 (SAEDON_TOKEN=wrong)</t>
+        </is>
+      </c>
+      <c r="E16" s="74" t="inlineStr">
+        <is>
+          <t>Claude Desktop에 MCP 서버는 등록됐지만 토큰이 유효하지 않음</t>
+        </is>
+      </c>
+      <c r="F16" s="74" t="inlineStr">
+        <is>
+          <t>Claude에게 "나 지금 뭐 구독하고 있어?" 질문</t>
+        </is>
+      </c>
+      <c r="G16" s="75" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="H16" s="74" t="inlineStr">
+        <is>
+          <t>도구 오류 "서비스 연결 토큰이 유효하지 않습니다. 토큰 확인이 필요합니다." → 에이전트가 토큰 확인을 안내, 결제 데이터는 노출되지 않음</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
       <c r="J16" s="1" t="n"/>
       <c r="K16" s="24" t="n"/>
     </row>
